--- a/lcr_analyses/clustering/carriers/SEG_intermediate/cluster_summaries_pam.xlsx
+++ b/lcr_analyses/clustering/carriers/SEG_intermediate/cluster_summaries_pam.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4488,4 +4492,5734 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>132</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.08259658893143057</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.58333333333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2651515151515151</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09848484848484848</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9621212121212122</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.09848484848484848</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2196969696969697</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.09848484848484848</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.007575757575757576</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.007575757575757576</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.8560606060606061</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.03787878787878788</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4026143790849673</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08257271510283559</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.09521292660827545</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1961538461538461</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.02617174136161476</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.213021778584392</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>73</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>113</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.04698972099853157</v>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05309734513274336</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.02654867256637168</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1858407079646018</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1415929203539823</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5221238938053098</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02654867256637168</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01769911504424779</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05309734513274336</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.02654867256637168</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.02654867256637168</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.02654867256637168</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.008849557522123894</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.008849557522123894</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.01769911504424779</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.06194690265486726</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.008849557522123894</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.008849557522123894</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.07500000000000002</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.5865921787709497</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.651685393258427</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.53125</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1310344827586207</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>69</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1740412979351033</v>
+      </c>
+      <c r="E4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1739130434782609</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7101449275362319</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1884057971014493</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.855072463768116</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.01449275362318841</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01449275362318841</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1159420289855072</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.05797101449275362</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.4661016949152542</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5932203389830508</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.103125</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.06726457399103138</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8105263157894737</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1981132075471699</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.03424657534246575</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2361111111111111</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.1739130434782609</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2057213722956355</v>
+      </c>
+      <c r="E5" t="n">
+        <v>41.58333333333333</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4305555555555556</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1805555555555556</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.09722222222222222</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8567629179331306</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.2552105948762484</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.06137048192771084</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.05031645569620254</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8443637341942427</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.3722864145658263</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.09279336734693877</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.4464646464646465</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.2729132569558101</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3238545816733068</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>56</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05215827338129497</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3238095238095238</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.3095238095238095</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>66</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05424043144416951</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07575757575757576</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.07575757575757576</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.07575757575757576</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1060606060606061</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6515151515151515</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1060606060606061</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2878787878787879</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.8559907834101382</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5124316939890711</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.0717142857142857</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.01793650793650794</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.2223320158102767</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.6742424242424242</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.2394067796610169</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.08444444444444446</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>65</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07552870090634441</v>
+      </c>
+      <c r="E8" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04615384615384616</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2153846153846154</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1692307692307692</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6461538461538462</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1846153846153846</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01538461538461539</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.04615384615384616</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8307692307692308</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.01538461538461539</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1636363636363637</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1052631578947369</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7230769230769231</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.01538461538461538</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.04615384615384616</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>4.440892098500626e-18</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>39</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>127</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.08235294117647059</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03937007874015748</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.06299212598425197</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2677165354330709</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1023622047244094</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.968503937007874</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1181102362204724</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.07874015748031496</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1889763779527559</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.06299212598425197</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1023622047244094</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2204724409448819</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.03149606299212598</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.09448818897637795</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.007874015748031496</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1181102362204724</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.007874015748031496</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.01574803149606299</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.8503937007874016</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.03149606299212598</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.03937007874015748</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.01834862385321101</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1891891891891892</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.02325581395348837</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>69</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>35</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.05845511482254697</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2456140350877193</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.1403508771929824</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.07017543859649122</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.4108527131782946</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.2418300653594771</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1737553428451026</v>
+      </c>
+      <c r="E4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1857142857142857</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1571428571428571</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3285714285714286</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.4663841807909604</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5932203389830508</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1019826680672269</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.07850877192982456</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8115131578947368</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2212806026365349</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.03413009039232132</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2366996233521657</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.1830357142857143</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.4791304347826087</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>65</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2302904564315353</v>
+      </c>
+      <c r="E5" t="n">
+        <v>45</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6461538461538462</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01538461538461539</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9846153846153847</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.04615384615384616</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1384615384615385</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1230769230769231</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.01538461538461539</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.2153846153846154</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.04824561403508772</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.847457627118644</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.07804878048780488</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.4553571428571428</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3208955223880597</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>53</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>109</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05215827338129497</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.06422018348623854</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1284403669724771</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3302752293577982</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1651376146788991</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.09174311926605505</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.009174311926605505</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.009174311926605505</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.08256880733944955</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.01834862385321101</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05504587155963303</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.04587155963302753</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02752293577981652</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.02752293577981652</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.05504587155963303</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.009174311926605505</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.8165137614678899</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.01834862385321101</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.009174311926605505</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.01834862385321101</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.009174311926605505</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.06422018348623854</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>62</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>59</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04669260700389105</v>
+      </c>
+      <c r="E7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.06779661016949153</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1016949152542373</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6440677966101694</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.05084745762711865</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.01694915254237288</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.7288135593220338</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3220338983050847</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1694915254237288</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1355932203389831</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01694915254237288</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.01694915254237288</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.01694915254237288</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5490196078431373</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.07303370786516854</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.005617977528089887</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1914893617021277</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.6612903225806451</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>65</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07552870090634441</v>
+      </c>
+      <c r="E8" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04615384615384616</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2153846153846154</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1692307692307692</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6461538461538462</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1846153846153846</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01538461538461539</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.04615384615384616</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8307692307692308</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.01538461538461539</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1636363636363637</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1052631578947369</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7230769230769231</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.01538461538461538</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.04615384615384616</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>4.440892098500626e-18</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>39</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.04403068862275449</v>
+      </c>
+      <c r="E9" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1571428571428571</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1285714285714286</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.8441295546558705</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.2020373514431239</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.07500000000000001</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.01870281400137268</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7071428571428571</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0140625</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.6318879855465221</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.6733333333333333</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.6172161172161172</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1201298701298701</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>117</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.08284023668639054</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04273504273504274</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1025641025641026</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9658119658119658</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1196581196581197</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1367521367521368</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.06837606837606838</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2393162393162393</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.03418803418803419</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.09401709401709402</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.008547008547008548</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1282051282051282</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.008547008547008548</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.0170940170940171</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9145299145299145</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.03418803418803419</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.04273504273504274</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.3853211009174312</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.09448818897637794</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8192771084337349</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.08888888888888891</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.07894736842105263</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>61</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.05845511482254697</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2545454545454545</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2181818181818182</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.1454545454545454</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1090909090909091</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.07272727272727272</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.07272727272727272</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1090909090909091</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1090909090909091</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.4108527131782946</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.2380952380952381</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>63</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1837606837606838</v>
+      </c>
+      <c r="E4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03174603174603174</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6825396825396826</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1587301587301587</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3650793650793651</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9206349206349206</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.03174603174603174</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.03174603174603174</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01587301587301587</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.03174603174603174</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.4661016949152542</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.103125</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.07368421052631577</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.03424657534246575</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.1940298507462687</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.452914798206278</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>64</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2335662808473466</v>
+      </c>
+      <c r="E5" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.078125</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.015625</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.984375</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.078125</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.140625</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.078125</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.015625</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8684860736747529</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.05277777777777778</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.04887528226506861</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8481732580037664</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.3827838827838828</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.07748592870544091</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.4521683673469388</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.2834821428571428</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3148595258999122</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>52</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05316188534958186</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1346153846153846</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3557692307692308</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1730769230769231</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.09615384615384616</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.009615384615384616</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.009615384615384616</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02884615384615385</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0576923076923077</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.04807692307692308</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02884615384615385</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.02884615384615385</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.009615384615384616</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.009615384615384616</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.009615384615384616</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.009615384615384616</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.0673076923076923</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.3114224137931034</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7824960576706466</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.0291289592760181</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1094348659003831</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>61</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>59</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04669260700389105</v>
+      </c>
+      <c r="E7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.06779661016949153</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1016949152542373</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6440677966101694</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.05084745762711865</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.01694915254237288</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.7288135593220338</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3220338983050847</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1694915254237288</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1355932203389831</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01694915254237288</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.01694915254237288</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.01694915254237288</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5490196078431373</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.07303370786516854</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.005617977528089887</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1914893617021277</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.6612903225806451</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06628242074927954</v>
+      </c>
+      <c r="E8" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1929824561403509</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1228070175438596</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7192982456140351</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.07017543859649122</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.08771929824561403</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.08771929824561403</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8596491228070176</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.2982456140350877</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.07017543859649122</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.005208333333333332</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>35</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.04403068862275449</v>
+      </c>
+      <c r="E9" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1571428571428571</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1285714285714286</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.8441295546558705</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.2020373514431239</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.07500000000000001</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.01870281400137268</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7071428571428571</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0140625</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.6318879855465221</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.6733333333333333</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.6172161172161172</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1201298701298701</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>33</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="E10" t="n">
+        <v>26</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.05714285714285712</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.05042016806722689</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.09803921568627452</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.01680672268907563</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>94</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.08308678500986194</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05319148936170213</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2659574468085106</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0425531914893617</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9680851063829787</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1170212765957447</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1170212765957447</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1063829787234043</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0851063829787234</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.09574468085106383</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.01063829787234043</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1276595744680851</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.01063829787234043</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.0425531914893617</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4438095238095238</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4324324324324324</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.09612651030561478</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.01732377538829152</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8230630055342699</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1040540540540541</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.04536117767887711</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.05228981544771018</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>54</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.04857330792959536</v>
+      </c>
+      <c r="E3" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08928571428571429</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3035714285714285</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01785714285714286</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9464285714285714</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.01785714285714286</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01785714285714286</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.875484496124031</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1936734183545887</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.05131578947368421</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7928571428571429</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.03869047619047618</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1067241379310345</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>62</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.185405521736457</v>
+      </c>
+      <c r="E4" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1774193548387097</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6935483870967742</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3709677419354839</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9516129032258065</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1129032258064516</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.4661016949152542</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.583916083916084</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1034492924528302</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.06724573237366695</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8115131578947368</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2256944444444445</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.03431078767123288</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2372881355932203</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.192603160667252</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.4561871288328687</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>39</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2043478260869565</v>
+      </c>
+      <c r="E5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.05970149253731343</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.08955223880597014</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6268656716417911</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05970149253731343</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4029850746268657</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02985074626865672</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8955223880597015</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.04477611940298507</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.04477611940298507</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1641791044776119</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1343283582089552</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.05970149253731343</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.04477611940298507</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.04477611940298507</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1492537313432836</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.05594405594405596</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.05063291139240506</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.84765625</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.07692307692307694</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05255888746946368</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08163265306122448</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1836734693877551</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1020408163265306</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.01020408163265306</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03061224489795918</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03061224489795918</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.03061224489795918</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.03061224489795918</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.03061224489795918</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.06122448979591837</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.01020408163265306</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01020408163265306</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.06122448979591837</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.2928571428571429</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.6066176470588236</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1143790849673202</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7824960576706466</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.05409356725146199</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1188235294117647</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>61</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04679144385026738</v>
+      </c>
+      <c r="E7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08196721311475409</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.08196721311475409</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.08196721311475409</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1147540983606557</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6721311475409836</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1147540983606557</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6885245901639344</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3114754098360656</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1311475409836066</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1311475409836066</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1955555555555555</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.2666666666666666</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.08000000000000003</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06766501989844929</v>
+      </c>
+      <c r="E8" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05357142857142857</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1964285714285714</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.08928571428571429</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01785714285714286</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.01785714285714286</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.08928571428571429</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.01785714285714286</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.5206837606837607</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7459677419354839</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.03390804597701149</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.03960784313725491</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.005413155430711607</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>55</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.04514363885088919</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.07272727272727272</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.07272727272727272</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.02479338842975207</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7254901960784313</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.5416666666666666</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1376811594202899</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>32</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0815945698197215</v>
+      </c>
+      <c r="E10" t="n">
+        <v>26</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.4950980392156863</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.05741758241758241</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.04459016393442623</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.8514705882352941</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.05042016806722689</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.02181050656660413</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.09157279933249898</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.01680672268907563</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.6088235294117648</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>41</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1039106145251397</v>
+      </c>
+      <c r="E11" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3170731707317073</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2682926829268293</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9024390243902439</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1219512195121951</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1707317073170732</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1463414634146341</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1463414634146341</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.5972222222222222</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.360655737704918</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.09398496240601505</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.02061855670103093</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.8192771084337349</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1075268817204301</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.2213114754098361</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.3440860215053764</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.0769230769230769</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1654135338345865</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>